--- a/Test_Results/Security/web-security-findings.xlsx
+++ b/Test_Results/Security/web-security-findings.xlsx
@@ -209,7 +209,7 @@
     <t>Generated At</t>
   </si>
   <si>
-    <t>2026-07-28T03:54:26.557Z</t>
+    <t>2026-07-28T03:56:37.008Z</t>
   </si>
 </sst>
 </file>
